--- a/artfynd/A 58085-2024 artfynd.xlsx
+++ b/artfynd/A 58085-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80685778</v>
+        <v>80685772</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545064.2157624941</v>
+        <v>545283</v>
       </c>
       <c r="R2" t="n">
-        <v>6974355.079300549</v>
+        <v>6974626</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-10-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80685780</v>
+        <v>80925665</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545054.9456162256</v>
+        <v>545417</v>
       </c>
       <c r="R3" t="n">
-        <v>6974364.984663473</v>
+        <v>6974546</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,21 +840,11 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -883,53 +853,53 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80685769</v>
+        <v>80925700</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545181.8484156579</v>
+        <v>545331</v>
       </c>
       <c r="R4" t="n">
-        <v>6974831.870086248</v>
+        <v>6974373</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,21 +942,11 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -995,31 +955,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80685783</v>
+        <v>80925743</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545255.8186648507</v>
+        <v>545153</v>
       </c>
       <c r="R5" t="n">
-        <v>6974303.910073573</v>
+        <v>6974797</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,21 +1044,11 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1107,53 +1057,53 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80685781</v>
+        <v>80685771</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545272.161864599</v>
+        <v>545386</v>
       </c>
       <c r="R6" t="n">
-        <v>6974310.977034906</v>
+        <v>6974588</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1146,9 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-10-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80685775</v>
+        <v>80685773</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545133.1748869708</v>
+        <v>545351</v>
       </c>
       <c r="R7" t="n">
-        <v>6974355.117853269</v>
+        <v>6974353</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1243,9 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-10-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>80685782</v>
+        <v>80925704</v>
       </c>
       <c r="B8" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545186.9812272728</v>
+        <v>545441</v>
       </c>
       <c r="R8" t="n">
-        <v>6974328.041528709</v>
+        <v>6974342</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,21 +1340,11 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1443,53 +1353,53 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>80685777</v>
+        <v>80925710</v>
       </c>
       <c r="B9" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545059.1806055511</v>
+        <v>545374</v>
       </c>
       <c r="R9" t="n">
-        <v>6974355.922040856</v>
+        <v>6974341</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,21 +1442,11 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1555,53 +1455,53 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Lutande sälg</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>80685772</v>
+        <v>80925699</v>
       </c>
       <c r="B10" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545282.8747287216</v>
+        <v>545271</v>
       </c>
       <c r="R10" t="n">
-        <v>6974625.788438638</v>
+        <v>6974376</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1544,9 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2019-10-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,49 +1561,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>80685776</v>
+        <v>80925750</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545153.1422191323</v>
+        <v>545118</v>
       </c>
       <c r="R11" t="n">
-        <v>6974331.222719405</v>
+        <v>6974590</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,19 +1641,14 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Välspridd, måttligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1779,53 +1659,53 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>80685779</v>
+        <v>80685782</v>
       </c>
       <c r="B12" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545052.1934679407</v>
+        <v>545187</v>
       </c>
       <c r="R12" t="n">
-        <v>6974365.858854701</v>
+        <v>6974328</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1748,9 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2019-10-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,37 +1777,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>80685771</v>
+        <v>80685775</v>
       </c>
       <c r="B13" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545386.1451902931</v>
+        <v>545133</v>
       </c>
       <c r="R13" t="n">
-        <v>6974588.002428192</v>
+        <v>6974355</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,19 +1845,9 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2019-10-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,15 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>80925700</v>
+        <v>80685776</v>
       </c>
       <c r="B14" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,21 +1885,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545331.1305974349</v>
+        <v>545153</v>
       </c>
       <c r="R14" t="n">
-        <v>6974372.904473898</v>
+        <v>6974331</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,21 +1942,11 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2115,58 +1955,48 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>80925666</v>
+        <v>80685778</v>
       </c>
       <c r="B15" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545457.8448768799</v>
+        <v>545064</v>
       </c>
       <c r="R15" t="n">
-        <v>6974554.796539454</v>
+        <v>6974355</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2209,24 +2039,9 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2019-10-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Måttligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,27 +2056,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>80925668</v>
+        <v>80685780</v>
       </c>
       <c r="B16" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,10 +2103,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545406.9058988896</v>
+        <v>545055</v>
       </c>
       <c r="R16" t="n">
-        <v>6974572.785915998</v>
+        <v>6974365</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2326,21 +2136,11 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2349,36 +2149,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Grov asp</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>80925731</v>
+        <v>80685781</v>
       </c>
       <c r="B17" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,10 +2200,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545117.1841994893</v>
+        <v>545272</v>
       </c>
       <c r="R17" t="n">
-        <v>6974819.121911531</v>
+        <v>6974311</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2443,21 +2233,11 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2466,36 +2246,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Knäckt grov sälg</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>80925665</v>
+        <v>80685783</v>
       </c>
       <c r="B18" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,21 +2273,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2527,10 +2297,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545416.8673379067</v>
+        <v>545256</v>
       </c>
       <c r="R18" t="n">
-        <v>6974546.018939927</v>
+        <v>6974304</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2560,21 +2330,11 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2583,36 +2343,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>80925751</v>
+        <v>80925668</v>
       </c>
       <c r="B19" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2620,21 +2370,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2644,10 +2394,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545163.0792058727</v>
+        <v>545407</v>
       </c>
       <c r="R19" t="n">
-        <v>6974636.900544113</v>
+        <v>6974573</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2677,21 +2427,11 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2703,7 +2443,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Grov asp</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2721,37 +2461,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>80925744</v>
+        <v>80925695</v>
       </c>
       <c r="B20" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2761,10 +2496,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545174.0715706106</v>
+        <v>545352</v>
       </c>
       <c r="R20" t="n">
-        <v>6974799.843733326</v>
+        <v>6974352</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2794,26 +2529,11 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Måttligt</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2822,6 +2542,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2838,15 +2563,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>80925740</v>
+        <v>80925703</v>
       </c>
       <c r="B21" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2854,43 +2574,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storåsen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545175.1166937494</v>
+        <v>545436</v>
       </c>
       <c r="R21" t="n">
-        <v>6974658.043142514</v>
+        <v>6974355</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2920,21 +2631,11 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2943,6 +2644,11 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Sälglåga</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2959,15 +2665,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>80925743</v>
+        <v>80925707</v>
       </c>
       <c r="B22" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,21 +2676,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2999,10 +2700,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545153.1085993726</v>
+        <v>545378</v>
       </c>
       <c r="R22" t="n">
-        <v>6974796.81835575</v>
+        <v>6974342</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3032,21 +2733,11 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3058,7 +2749,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Lutande sälg</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3076,37 +2767,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>80925752</v>
+        <v>80925716</v>
       </c>
       <c r="B23" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3116,10 +2802,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545136.8000203163</v>
+        <v>545438</v>
       </c>
       <c r="R23" t="n">
-        <v>6974621.945478409</v>
+        <v>6974341</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3149,21 +2835,11 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3175,7 +2851,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Klen skadad sälg</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3193,37 +2869,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>80925667</v>
+        <v>80925731</v>
       </c>
       <c r="B24" t="n">
-        <v>77756</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3233,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545406.9185565353</v>
+        <v>545117</v>
       </c>
       <c r="R24" t="n">
-        <v>6974571.87405242</v>
+        <v>6974819</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3266,21 +2937,11 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3292,7 +2953,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Grov asp</t>
+          <t>Knäckt grov sälg</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3310,15 +2971,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>80925703</v>
+        <v>80925746</v>
       </c>
       <c r="B25" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3350,10 +3006,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545435.9573421575</v>
+        <v>545138</v>
       </c>
       <c r="R25" t="n">
-        <v>6974355.204679918</v>
+        <v>6974792</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3383,21 +3039,11 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3409,7 +3055,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Sälglåga</t>
+          <t>Död sälg</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3427,15 +3073,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>80925746</v>
+        <v>80925754</v>
       </c>
       <c r="B26" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3467,10 +3108,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545138.105757624</v>
+        <v>545185</v>
       </c>
       <c r="R26" t="n">
-        <v>6974792.051404485</v>
+        <v>6974618</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3500,21 +3141,11 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3526,7 +3157,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Död sälg</t>
+          <t>Grov sälglåga</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3544,37 +3175,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>80925750</v>
+        <v>80925667</v>
       </c>
       <c r="B27" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3584,10 +3210,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>545118.0583061809</v>
+        <v>545407</v>
       </c>
       <c r="R27" t="n">
-        <v>6974590.221973676</v>
+        <v>6974572</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3617,26 +3243,11 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Välspridd, måttligt</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3648,7 +3259,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Grov asp</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3666,37 +3277,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>80925754</v>
+        <v>80925735</v>
       </c>
       <c r="B28" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3706,10 +3312,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545184.8020541182</v>
+        <v>545069</v>
       </c>
       <c r="R28" t="n">
-        <v>6974618.048079526</v>
+        <v>6974810</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3739,21 +3345,11 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3765,7 +3361,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Grov sälglåga</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3783,59 +3379,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>80925693</v>
+        <v>80925737</v>
       </c>
       <c r="B29" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6459</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storåsen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545354.1538684635</v>
+        <v>545063</v>
       </c>
       <c r="R29" t="n">
-        <v>6974589.838796843</v>
+        <v>6974790</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3865,21 +3447,11 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3888,6 +3460,11 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3904,15 +3481,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>80925734</v>
+        <v>80685779</v>
       </c>
       <c r="B30" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3944,10 +3516,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545118.9851839313</v>
+        <v>545052</v>
       </c>
       <c r="R30" t="n">
-        <v>6974820.97069033</v>
+        <v>6974366</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3977,21 +3549,11 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4000,36 +3562,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Knäckt grov sälg</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>80925699</v>
+        <v>80925734</v>
       </c>
       <c r="B31" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4061,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545270.8029576188</v>
+        <v>545119</v>
       </c>
       <c r="R31" t="n">
-        <v>6974376.173498998</v>
+        <v>6974821</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4094,21 +3646,11 @@
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2019-10-15</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4117,6 +3659,11 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Knäckt grov sälg</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4130,6 +3677,1334 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>80925698</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>545354</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6974353</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>80925709</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>545379</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6974341</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Lutande sälg</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>80925696</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>545376</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6974345</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Lutande sälg</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>80925723</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>545061</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6974792</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>80925752</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>545137</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6974622</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Klen skadad sälg</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>80925693</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>545354</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6974590</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>80925740</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>545175</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6974658</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>80685769</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>545182</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6974832</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>80925708</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>545446</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6974367</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>80685777</v>
+      </c>
+      <c r="B41" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>545059</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6974356</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>80925666</v>
+      </c>
+      <c r="B42" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>545458</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6974555</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Måttligt</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>80925744</v>
+      </c>
+      <c r="B43" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>545174</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6974800</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Måttligt</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>80925724</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>545064</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6974793</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58085-2024 artfynd.xlsx
+++ b/artfynd/A 58085-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80685772</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925665</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925700</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925743</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80685771</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,6 +1299,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80685773</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925704</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925710</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925699</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1677,6 +1727,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925750</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1774,6 +1829,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80685782</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1871,6 +1931,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80685775</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1968,6 +2033,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80685776</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2065,6 +2135,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80685778</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2162,6 +2237,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80685780</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2259,6 +2339,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80685781</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2356,6 +2441,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80685783</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2458,6 +2548,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925668</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2560,6 +2655,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925695</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2662,6 +2762,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925703</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2764,6 +2869,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925707</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2866,6 +2976,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925716</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2968,6 +3083,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925731</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3070,6 +3190,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925746</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3172,6 +3297,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925754</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3274,6 +3404,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925667</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3376,6 +3511,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925735</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3478,6 +3618,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925737</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3575,6 +3720,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80685779</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3677,6 +3827,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925734</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3779,6 +3934,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925698</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3881,6 +4041,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925709</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3983,6 +4148,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925696</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4085,6 +4255,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925723</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4187,6 +4362,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925752</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4293,6 +4473,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925693</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4399,6 +4584,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925740</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4496,6 +4686,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80685769</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4602,6 +4797,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925708</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4699,6 +4899,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80685777</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4801,6 +5006,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925666</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4903,6 +5113,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925744</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5005,8 +5220,58 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925724</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>